--- a/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_7_7.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_7_7.xlsx
@@ -517,1317 +517,1317 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9999999983044463</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6649601230980053</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9999999999084707</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E2" t="n">
-        <v>0.999999999143081</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999999995972582</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G2" t="n">
-        <v>1.006553903094363e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1988941438981106</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I2" t="n">
-        <v>4.447468896557214e-11</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>2.853916593611713e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K2" t="n">
-        <v>1.651937062894971e-10</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>9.001388452122535e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.172623367332408e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000000000992519</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O2" t="n">
-        <v>3.307688512315503e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P2" t="n">
-        <v>171.4334666345916</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q2" t="n">
-        <v>250.6603952510246</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_1</t>
+          <t>model_7_7_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9999999985837749</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6649367932750112</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9999999997470571</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999999992251175</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999999995364333</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G3" t="n">
-        <v>8.407324394819173e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1989079934888359</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I3" t="n">
-        <v>1.229065612687258e-10</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>2.580698882234311e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>1.901424274916619e-10</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>8.567766752667282e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.899538652065044e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N3" t="n">
-        <v>1.00000000082901</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O3" t="n">
-        <v>3.022978015355915e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P3" t="n">
-        <v>171.7934953045122</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q3" t="n">
-        <v>251.0204239209452</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_2</t>
+          <t>model_7_7_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9999999987889063</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6649132562136378</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9999999994793279</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9999999992508355</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9999999993874501</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G4" t="n">
-        <v>7.18957502629147e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1989219661052152</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I4" t="n">
-        <v>2.529978150314335e-10</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>2.49504685103507e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>2.512512500674702e-10</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>8.009281317017042e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>2.681338290162483e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000000000708933</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O4" t="n">
-        <v>2.795488412310144e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P4" t="n">
-        <v>172.106437732345</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q4" t="n">
-        <v>251.333366348778</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_4</t>
+          <t>model_7_7_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9999999992363506</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6649073075071641</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9999999994509949</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9999999987563124</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9999999991699013</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G5" t="n">
-        <v>4.533352429612869e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1989254975143487</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I5" t="n">
-        <v>2.667650176890204e-10</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>4.142025898932101e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>3.404838037911153e-10</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>6.219885098181004e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>2.129167074142579e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000000000447014</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O5" t="n">
-        <v>2.21981012447228e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P5" t="n">
-        <v>173.0287784269217</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q5" t="n">
-        <v>252.2557070433547</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_3</t>
+          <t>model_7_7_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9999999989486859</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6648995474049417</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9999999992668017</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E6" t="n">
-        <v>0.999999999261864</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9999999992673722</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G6" t="n">
-        <v>6.241054913931284e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1989301042462469</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I6" t="n">
-        <v>3.562656624844297e-10</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>2.458316990814999e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>3.005039315625354e-10</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>7.6646252430915e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>2.498210342211256e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000000000615404</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O6" t="n">
-        <v>2.604564328487522e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P6" t="n">
-        <v>172.3894034102557</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q6" t="n">
-        <v>251.6163320266887</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_5</t>
+          <t>model_7_7_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9999999992745857</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6648944681628284</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9999999991916226</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9999999984524564</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9999999988929107</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G7" t="n">
-        <v>4.306372285257947e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1989331195037772</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I7" t="n">
-        <v>3.927956730076011e-10</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.154000095928823e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K7" t="n">
-        <v>4.540978413002417e-10</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>6.148265663632747e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.07518006092434e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000000000424633</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O7" t="n">
-        <v>2.163524772332817e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P7" t="n">
-        <v>173.1315101548134</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q7" t="n">
-        <v>252.3584387712464</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_6</t>
+          <t>model_7_7_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9999999993254484</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6648820997970653</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9999999990081386</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9999999982746749</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9999999987111415</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G8" t="n">
-        <v>4.004429793681026e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1989404618999798</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I8" t="n">
-        <v>4.81951677100562e-10</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>5.746090340965971e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K8" t="n">
-        <v>5.286545745624265e-10</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>5.947221015310139e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.001107141979416e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000000000394859</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O8" t="n">
-        <v>2.086298415876327e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P8" t="n">
-        <v>173.2768994663379</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q8" t="n">
-        <v>252.503828082771</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_8</t>
+          <t>model_7_7_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9999999985499934</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6646496745862656</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9999999911748855</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9999999982125343</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9999999940470402</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G9" t="n">
-        <v>8.607865158016024e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1990784395453568</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I9" t="n">
-        <v>4.288178776656292e-09</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>5.953046115049311e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K9" t="n">
-        <v>2.441741694080612e-09</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>7.196466147299832e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>2.933916351571057e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000000000848784</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O9" t="n">
-        <v>3.058819244701548e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P9" t="n">
-        <v>171.7463491827447</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q9" t="n">
-        <v>250.9732777991777</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_10</t>
+          <t>model_7_7_15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.999999998649945</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C10" t="n">
-        <v>0.664649426405622</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9999999912220225</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9999999984026346</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9999999941521374</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G10" t="n">
-        <v>8.014509739554541e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1990785868761077</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I10" t="n">
-        <v>4.265274581613739e-09</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J10" t="n">
-        <v>5.319928219456225e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K10" t="n">
-        <v>2.398633701779681e-09</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L10" t="n">
-        <v>6.274905221493896e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>2.830990946568805e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000000000790276</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O10" t="n">
-        <v>2.95151209212339e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P10" t="n">
-        <v>171.8891946272314</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q10" t="n">
-        <v>251.1161232436644</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_12</t>
+          <t>model_7_7_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.999999998526822</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6646405644947044</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9999999904062048</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9999999980314153</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9999999935229286</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G11" t="n">
-        <v>8.745421150000061e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1990838476892429</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I11" t="n">
-        <v>4.66168556542115e-09</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J11" t="n">
-        <v>6.556251897367218e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K11" t="n">
-        <v>2.656717964596417e-09</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L11" t="n">
-        <v>6.276547130662949e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>2.957265823357796e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000000000862348</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O11" t="n">
-        <v>3.083162751842317e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P11" t="n">
-        <v>171.714641327363</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q11" t="n">
-        <v>250.9415699437961</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_9</t>
+          <t>model_7_7_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9999999985673084</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6646404736209454</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9999999909146454</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9999999982842163</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9999999939219965</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G12" t="n">
-        <v>8.505076517561772e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1990839016358319</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I12" t="n">
-        <v>4.414631065123734e-09</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J12" t="n">
-        <v>5.714313428216696e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K12" t="n">
-        <v>2.493031203972702e-09</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L12" t="n">
-        <v>6.855102060559464e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>2.916346433049711e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000000000838649</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O12" t="n">
-        <v>3.040501338374002e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P12" t="n">
-        <v>171.7703754147185</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q12" t="n">
-        <v>250.9973040311515</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_11</t>
+          <t>model_7_7_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9999999985218991</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6646352114171061</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9999999903518714</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9999999981344569</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9999999935322192</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G13" t="n">
-        <v>8.774645482469813e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1990870255073462</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I13" t="n">
-        <v>4.68808649040802e-09</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J13" t="n">
-        <v>6.2130777175442e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K13" t="n">
-        <v>2.652907166472472e-09</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L13" t="n">
-        <v>6.274694265129187e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>2.962202809138803e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N13" t="n">
-        <v>1.00000000086523</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O13" t="n">
-        <v>3.088309915328992e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P13" t="n">
-        <v>171.7079691245256</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q13" t="n">
-        <v>250.9348977409587</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_7</t>
+          <t>model_7_7_12</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9999999983817837</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6646282766790366</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9999999904762935</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9999999978572606</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9999999934917495</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G14" t="n">
-        <v>9.606430905043767e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1990911422674294</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I14" t="n">
-        <v>4.627629003248027e-09</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J14" t="n">
-        <v>7.136263591116963e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K14" t="n">
-        <v>2.669506789258099e-09</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L14" t="n">
-        <v>7.784165299805054e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>3.09942428606407e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000000000947249</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O14" t="n">
-        <v>3.231373194614584e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P14" t="n">
-        <v>171.5268363395961</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q14" t="n">
-        <v>250.7537649560291</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_13</t>
+          <t>model_7_7_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9999999985331536</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6646138773015071</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9999999902627256</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9999999981995655</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9999999934969005</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G15" t="n">
-        <v>8.707834071758848e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1990996903599516</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I15" t="n">
-        <v>4.731403029565552e-09</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J15" t="n">
-        <v>5.996237477772562e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K15" t="n">
-        <v>2.667393958235063e-09</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L15" t="n">
-        <v>6.099028305640186e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>2.950903941465877e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000000000858642</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O15" t="n">
-        <v>3.076530031467349e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P15" t="n">
-        <v>171.7232556828795</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q15" t="n">
-        <v>250.9501842993126</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_14</t>
+          <t>model_7_7_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.99999999845198</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6646071289361901</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9999999897074084</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9999999980743447</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9999999931144757</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G16" t="n">
-        <v>9.18971560789591e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H16" t="n">
-        <v>0.199103696481118</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I16" t="n">
-        <v>5.001235127664819e-09</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J16" t="n">
-        <v>6.413277971331576e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K16" t="n">
-        <v>2.824254189876195e-09</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L16" t="n">
-        <v>6.213822167982973e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.031454371732471e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000000000906158</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O16" t="n">
-        <v>3.16050966031277e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P16" t="n">
-        <v>171.6155318797474</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q16" t="n">
-        <v>250.8424604961804</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_15</t>
+          <t>model_7_7_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9999999984637608</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6646019882216542</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9999999897132151</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9999999981282939</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9999999931423068</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G17" t="n">
-        <v>9.119779651423509e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1991067482313338</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I17" t="n">
-        <v>4.998413619604237e-09</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J17" t="n">
-        <v>6.233603633986013e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K17" t="n">
-        <v>2.812838615338654e-09</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L17" t="n">
-        <v>5.987240238369524e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.01989729153551e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000000000899262</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O17" t="n">
-        <v>3.14846057128537e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P17" t="n">
-        <v>171.6308105743485</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q17" t="n">
-        <v>250.8577391907815</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_16</t>
+          <t>model_7_7_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9999999984669377</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6645963257384957</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9999999896929203</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9999999981583588</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F18" t="n">
-        <v>0.999999993154272</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G18" t="n">
-        <v>9.100920374521712e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1991101097259432</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I18" t="n">
-        <v>5.008274987208487e-09</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J18" t="n">
-        <v>6.133474206315267e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K18" t="n">
-        <v>2.80793084699845e-09</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L18" t="n">
-        <v>5.829137536242612e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M18" t="n">
-        <v>3.016773172534142e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000000000897402</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O18" t="n">
-        <v>3.145203452070296e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P18" t="n">
-        <v>171.6349507629493</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q18" t="n">
-        <v>250.8618793793823</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_17</t>
+          <t>model_7_7_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9999999984146425</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6645905728661092</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9999999893294723</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9999999980709673</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9999999928964932</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G19" t="n">
-        <v>9.411366711279344e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H19" t="n">
-        <v>0.199113524879503</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I19" t="n">
-        <v>5.184876671427604e-09</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J19" t="n">
-        <v>6.424526175776357e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K19" t="n">
-        <v>2.91366464450262e-09</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L19" t="n">
-        <v>5.921900079510302e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M19" t="n">
-        <v>3.0677950895194e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000000000928014</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O19" t="n">
-        <v>3.198397477691544e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P19" t="n">
-        <v>171.5678654931671</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q19" t="n">
-        <v>250.7947941096001</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_18</t>
+          <t>model_7_7_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9999999984111401</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6645841458172617</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9999999892235465</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9999999981513462</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9999999928663836</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G20" t="n">
-        <v>9.432158815384896e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H20" t="n">
-        <v>0.199117340253333</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I20" t="n">
-        <v>5.236346681799247e-09</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J20" t="n">
-        <v>6.156829192170628e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K20" t="n">
-        <v>2.926014800508155e-09</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L20" t="n">
-        <v>5.819477831241789e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.071181989948641e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000000000930064</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O20" t="n">
-        <v>3.201928565483909e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P20" t="n">
-        <v>171.5634518578281</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q20" t="n">
-        <v>250.7903804742612</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_19</t>
+          <t>model_7_7_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9999999983861975</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6645802087277058</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D21" t="n">
-        <v>0.999999989060375</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E21" t="n">
-        <v>0.999999998080371</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9999999927409194</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G21" t="n">
-        <v>9.580228835610475e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1991196774797667</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I21" t="n">
-        <v>5.315632727264496e-09</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J21" t="n">
-        <v>6.393207957427253e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K21" t="n">
-        <v>2.977476761503611e-09</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L21" t="n">
-        <v>5.837785226339513e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M21" t="n">
-        <v>3.095194474602601e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000000000944665</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O21" t="n">
-        <v>3.226963311322284e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P21" t="n">
-        <v>171.5322989028721</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q21" t="n">
-        <v>250.7592275193051</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_20</t>
+          <t>model_7_7_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9999999983444933</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6645753686568905</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9999999887675082</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9999999980224976</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9999999925439534</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G22" t="n">
-        <v>9.827803093070105e-10</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1991225507548829</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I22" t="n">
-        <v>5.45793853864188e-09</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J22" t="n">
-        <v>6.585951437973345e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K22" t="n">
-        <v>3.058266841219608e-09</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L22" t="n">
-        <v>5.789885660435144e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M22" t="n">
-        <v>3.134932709496347e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000000000969077</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O22" t="n">
-        <v>3.268393285144943e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P22" t="n">
-        <v>171.4812710215648</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q22" t="n">
-        <v>250.7081996379978</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_21</t>
+          <t>model_7_7_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9999999983105078</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6645698073040751</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9999999885712791</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9999999979029051</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9999999923737547</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G23" t="n">
-        <v>1.002955567577727e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H23" t="n">
-        <v>0.199125852214152</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I23" t="n">
-        <v>5.55328749538143e-09</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J23" t="n">
-        <v>6.984247328425028e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K23" t="n">
-        <v>3.12807774418879e-09</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L23" t="n">
-        <v>5.822267663718473e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M23" t="n">
-        <v>3.166947374961774e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000000000988971</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O23" t="n">
-        <v>3.301770881198727e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P23" t="n">
-        <v>171.4406292569431</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q23" t="n">
-        <v>250.6675578733762</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_22</t>
+          <t>model_7_7_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9999999982772443</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6645682511448245</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9999999883597218</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9999999978316888</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9999999922249492</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G24" t="n">
-        <v>1.022702208151985e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1991267760175058</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I24" t="n">
-        <v>5.656084526682793e-09</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J24" t="n">
-        <v>7.221428765976095e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K24" t="n">
-        <v>3.189113701640202e-09</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L24" t="n">
-        <v>5.831886050877213e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M24" t="n">
-        <v>3.197971557334407e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000000001008442</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O24" t="n">
-        <v>3.334115827243873e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P24" t="n">
-        <v>171.4016349779588</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q24" t="n">
-        <v>250.6285635943918</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_7_7_23</t>
+          <t>model_7_7_11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.999999998231799</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6645657862169065</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9999999880273688</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9999999978037918</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9999999920167645</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G25" t="n">
-        <v>1.0496805422631e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1991282393051972</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I25" t="n">
-        <v>5.817576948815356e-09</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J25" t="n">
-        <v>7.31433798084121e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K25" t="n">
-        <v>3.274505373449739e-09</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L25" t="n">
-        <v>5.81999239022118e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M25" t="n">
-        <v>3.239877377715244e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000000001035044</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O25" t="n">
-        <v>3.37780566515533e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P25" t="n">
-        <v>171.3495599290655</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q25" t="n">
-        <v>250.5764885454985</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9999999981674437</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6645621492826242</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9999999876418986</v>
+        <v>0.9999999856514609</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9999999976384272</v>
+        <v>0.9999999996696268</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9999999917153377</v>
+        <v>0.9999999961666223</v>
       </c>
       <c r="G26" t="n">
-        <v>1.087884630712785e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1991303983464945</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I26" t="n">
-        <v>6.004879339411561e-09</v>
+        <v>4.169031543589313e-09</v>
       </c>
       <c r="J26" t="n">
-        <v>7.865074649925041e-10</v>
+        <v>2.824428414642662e-10</v>
       </c>
       <c r="K26" t="n">
-        <v>3.398142405954299e-09</v>
+        <v>2.225725068694897e-09</v>
       </c>
       <c r="L26" t="n">
-        <v>5.933599385385166e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M26" t="n">
-        <v>3.29830961359419e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000000001072716</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O26" t="n">
-        <v>3.438725482287046e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P26" t="n">
-        <v>171.2780614641658</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q26" t="n">
-        <v>250.5049900805988</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
   </sheetData>
